--- a/artfynd/A 42835-2021 artfynd.xlsx
+++ b/artfynd/A 42835-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
+          <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens lä</t>
         </is>
       </c>
     </row>

--- a/artfynd/A 42835-2021 artfynd.xlsx
+++ b/artfynd/A 42835-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>88020959</v>
+        <v>88020957</v>
       </c>
       <c r="B2" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>476932.0402969845</v>
+        <v>476878</v>
       </c>
       <c r="R2" t="n">
-        <v>7258617.161049407</v>
+        <v>7258592</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -748,19 +743,9 @@
           <t>2020-09-15</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2020-09-15</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,15 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>88020961</v>
+        <v>88020963</v>
       </c>
       <c r="B3" t="n">
-        <v>101680</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89083</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222412</v>
+        <v>4377</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Blodvaxing</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Hygrocybe coccinea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Schaeff.) P.Kumm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -831,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>476892.8767216221</v>
+        <v>476899</v>
       </c>
       <c r="R3" t="n">
-        <v>7258562.971628867</v>
+        <v>7258483</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -864,19 +844,9 @@
           <t>2020-09-15</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2020-09-15</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,37 +877,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>88020960</v>
+        <v>88020959</v>
       </c>
       <c r="B4" t="n">
-        <v>95756</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222759</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Taggbräken</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Polystichum lonchitis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Roth</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -947,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>476889.1612766281</v>
+        <v>476932</v>
       </c>
       <c r="R4" t="n">
-        <v>7258567.161296669</v>
+        <v>7258617</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -980,19 +945,9 @@
           <t>2020-09-15</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2020-09-15</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,50 +978,50 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>88020963</v>
+        <v>88020956</v>
       </c>
       <c r="B5" t="n">
-        <v>86134</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4377</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blodvaxskivling</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hygrocybe coccinea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schaeff.) P.Kumm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Skalmodal, Ly lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>476898.9086861269</v>
+        <v>476886</v>
       </c>
       <c r="R5" t="n">
-        <v>7258483.045623574</v>
+        <v>7258355</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1096,19 +1051,9 @@
           <t>2020-09-15</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2020-09-15</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1139,55 +1084,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>88020956</v>
+        <v>88020962</v>
       </c>
       <c r="B6" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99142</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>219847</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Skalmodal, Ly lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>476885.8162237664</v>
+        <v>476895</v>
       </c>
       <c r="R6" t="n">
-        <v>7258355.006574076</v>
+        <v>7258562</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1217,19 +1152,9 @@
           <t>2020-09-15</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2020-09-15</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1260,15 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>88020962</v>
+        <v>88020961</v>
       </c>
       <c r="B7" t="n">
-        <v>96356</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104628</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1276,21 +1196,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219847</v>
+        <v>222412</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1300,10 +1220,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>476894.9525644757</v>
+        <v>476893</v>
       </c>
       <c r="R7" t="n">
-        <v>7258562.123150692</v>
+        <v>7258563</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1333,19 +1253,9 @@
           <t>2020-09-15</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2020-09-15</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1369,6 +1279,107 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr">
+        <is>
+          <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>88020960</v>
+      </c>
+      <c r="B8" t="n">
+        <v>98234</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>222759</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Taggbräken</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Polystichum lonchitis</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) Roth</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Skalmodal, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>476889</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7258567</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Tärna</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2020-09-15</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2020-09-15</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
         <is>
           <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
         </is>
